--- a/registration_forms/046_multi_email_registration_form--registration_forms.xlsx
+++ b/registration_forms/046_multi_email_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_111,_'name':_'team-1',_'label':_'team_1'}</t>
+          <t>team_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 111, 'name': 'team-1', 'label': 'Team 1'}</t>
+          <t>Team 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_112,_'name':_'team-2',_'label':_'team_2'}</t>
+          <t>team_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 112, 'name': 'team-2', 'label': 'Team 2'}</t>
+          <t>Team 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_113,_'name':_'team-3',_'label':_'team_3'}</t>
+          <t>team_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 113, 'name': 'team-3', 'label': 'Team 3'}</t>
+          <t>Team 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_114,_'name':_'team-4',_'label':_'team_4'}</t>
+          <t>team_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 114, 'name': 'team-4', 'label': 'Team 4'}</t>
+          <t>Team 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_121,_'name':_'training-1',_'label':_'training_1'}</t>
+          <t>training_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 121, 'name': 'training-1', 'label': 'Training 1'}</t>
+          <t>Training 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_122,_'name':_'training-2',_'label':_'training_2'}</t>
+          <t>training_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 122, 'name': 'training-2', 'label': 'Training 2'}</t>
+          <t>Training 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_123,_'name':_'training-3',_'label':_'training_3'}</t>
+          <t>training_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 123, 'name': 'training-3', 'label': 'Training 3'}</t>
+          <t>Training 3</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_141,_'name':_'assigned-1',_'label':_'assigned_1'}</t>
+          <t>assigned_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 141, 'name': 'assigned-1', 'label': 'Assigned 1'}</t>
+          <t>Assigned 1</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_142,_'name':_'assigned-2',_'label':_'assigned_2'}</t>
+          <t>assigned_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 142, 'name': 'assigned-2', 'label': 'Assigned 2'}</t>
+          <t>Assigned 2</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_171,_'name':_'follow_up-1',_'label':_'follow_up_1'}</t>
+          <t>follow_up_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 171, 'name': 'follow_up-1', 'label': 'Follow up 1'}</t>
+          <t>Follow up 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_172,_'name':_'follow_up-2',_'label':_'follow_up_2'}</t>
+          <t>follow_up_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 172, 'name': 'follow_up-2', 'label': 'Follow up 2'}</t>
+          <t>Follow up 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_173,_'name':_'follow_up-3',_'label':_'follow_up_3'}</t>
+          <t>follow_up_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 173, 'name': 'follow_up-3', 'label': 'Follow up 3'}</t>
+          <t>Follow up 3</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_174,_'name':_'follow_up-4',_'label':_'follow_up_4'}</t>
+          <t>follow_up_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 174, 'name': 'follow_up-4', 'label': 'Follow up 4'}</t>
+          <t>Follow up 4</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_181,_'name':_'follow_up_2-1',_'label':_'follow_up_2'}</t>
+          <t>follow_up_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 181, 'name': 'follow_up_2-1', 'label': 'Follow up 2'}</t>
+          <t>Follow up 2</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_182,_'name':_'follow_up_2-2',_'label':_'follow_up_2'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 182, 'name': 'follow_up_2-2', 'label': 'Follow up 2'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>follow_up_2_choices</t>
+          <t>workflow_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_183,_'name':_'follow_up_2-3',_'label':_'follow_up_2'}</t>
+          <t>workflow_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 183, 'name': 'follow_up_2-3', 'label': 'Follow up 2'}</t>
+          <t>Workflow 1</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_191,_'name':_'workflow-1',_'label':_'workflow_1'}</t>
+          <t>workflow_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 191, 'name': 'workflow-1', 'label': 'Workflow 1'}</t>
+          <t>Workflow 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>workflow_choices</t>
+          <t>event_id_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_192,_'name':_'workflow-2',_'label':_'workflow_2'}</t>
+          <t>event_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 192, 'name': 'workflow-2', 'label': 'Workflow 2'}</t>
+          <t>Event 1</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_201,_'name':_'event-1',_'label':_'event_1'}</t>
+          <t>event_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 201, 'name': 'event-1', 'label': 'Event 1'}</t>
+          <t>Event 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>event_id_choices</t>
+          <t>member_id_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_202,_'name':_'event-2',_'label':_'event_2'}</t>
+          <t>member_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 202, 'name': 'event-2', 'label': 'Event 2'}</t>
+          <t>Member 1</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_211,_'name':_'member-1',_'label':_'member_1'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 211, 'name': 'member-1', 'label': 'Member 1'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>member_id_choices</t>
+          <t>team_id_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>team_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Team 1</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_221,_'name':_'team-1',_'label':_'team_1'}</t>
+          <t>team_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 221, 'name': 'team-1', 'label': 'Team 1'}</t>
+          <t>Team 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>team_id_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_222,_'name':_'team-2',_'label':_'team_2'}</t>
+          <t>assigned_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 222, 'name': 'team-2', 'label': 'Team 2'}</t>
+          <t>Assigned 1</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_231,_'name':_'assigned-1',_'label':_'assigned_1'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 231, 'name': 'assigned-1', 'label': 'Assigned 1'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>follow_up_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>follow_up_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Follow up 3</t>
         </is>
       </c>
     </row>
@@ -1573,46 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_241,_'name':_'follow_up_3-1',_'label':_'follow_up_3'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 241, 'name': 'follow_up_3-1', 'label': 'Follow up 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>follow_up_3_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'id':_242,_'name':_'follow_up_3-2',_'label':_'follow_up_3'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'id': 242, 'name': 'follow_up_3-2', 'label': 'Follow up 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>follow_up_3_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_243,_'name':_'follow_up_3-3',_'label':_'follow_up_3'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 243, 'name': 'follow_up_3-3', 'label': 'Follow up 3'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
